--- a/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-EX-MarkingFlag.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-EX-MarkingFlag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1731,7 +1731,7 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
@@ -2250,7 +2250,7 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
@@ -2769,7 +2769,7 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
@@ -2977,7 +2977,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>121</v>
